--- a/artfynd/A 70738-2021 artfynd.xlsx
+++ b/artfynd/A 70738-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70738-2021 artfynd.xlsx
+++ b/artfynd/A 70738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56755349</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385567.1801922361</v>
+        <v>385567</v>
       </c>
       <c r="R2" t="n">
-        <v>6288545.810722203</v>
+        <v>6288546</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-06-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +778,122 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115687664</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klövabergets naturreservat, Simlångsdalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>385557</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6288469</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70738-2021 artfynd.xlsx
+++ b/artfynd/A 70738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755349</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115687664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>